--- a/sampleprojects/TaxReturn/excel/states/WV.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/WV.xlsx
@@ -71,7 +71,7 @@
     <t>WV tax = max(AGI - $0, 0) x 4.82%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 0.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0482</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 0.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0482</t>
   </si>
   <si>
     <t>X</t>
